--- a/data/trans_orig/IP07C18-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44195</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>61739</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45090</t>
+          <t>45513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62710</t>
+          <t>62697</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94319</t>
+          <t>94647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118950</t>
+          <t>118376</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,33%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35324</t>
+          <t>35678</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>37311</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52894</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75610</t>
+          <t>76517</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99847</t>
+          <t>99783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27677</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>24796</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42108</t>
+          <t>41968</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>57038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76924</t>
+          <t>77284</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45485</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65394</t>
+          <t>66656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108695</t>
+          <t>108473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138512</t>
+          <t>136896</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59649</t>
+          <t>60368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81031</t>
+          <t>81896</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>65268</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87863</t>
+          <t>87521</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131719</t>
+          <t>131755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161809</t>
+          <t>161486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22110</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38145</t>
+          <t>38165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48590</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58532</t>
+          <t>57795</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81409</t>
+          <t>82491</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15592</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>19196</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>107153</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133195</t>
+          <t>133447</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95034</t>
+          <t>95579</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>123528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211492</t>
+          <t>211827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249283</t>
+          <t>248763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101109</t>
+          <t>102148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127511</t>
+          <t>127650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108062</t>
+          <t>107611</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135311</t>
+          <t>134636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216361</t>
+          <t>215970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>255334</t>
+          <t>253998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54559</t>
+          <t>53354</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72002</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>24929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85699</t>
+          <t>84287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103981</t>
+          <t>104175</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82049</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103222</t>
+          <t>103494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173388</t>
+          <t>173504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201002</t>
+          <t>201504</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30473</t>
+          <t>30223</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47706</t>
+          <t>49066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32933</t>
+          <t>32941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68524</t>
+          <t>69064</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92437</t>
+          <t>93193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16063</t>
+          <t>15904</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1536</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10880</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69363</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90363</t>
+          <t>89813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65348</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86695</t>
+          <t>86881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140130</t>
+          <t>140849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170208</t>
+          <t>170947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>46070</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64751</t>
+          <t>65165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>60258</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82016</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112797</t>
+          <t>112242</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141625</t>
+          <t>140893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>28697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11123</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>28944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13371</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159797</t>
+          <t>160995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>189272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153968</t>
+          <t>153186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185066</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322703</t>
+          <t>321517</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364618</t>
+          <t>363346</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>80531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107695</t>
+          <t>106827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97654</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>127103</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>186192</t>
+          <t>188936</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227435</t>
+          <t>227984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22906</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>40350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48279</t>
+          <t>48450</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>73489</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12627</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8783</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20914</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con los profesores en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83741</t>
+          <t>84067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105668</t>
+          <t>105355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83621</t>
+          <t>85542</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105661</t>
+          <t>106231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174389</t>
+          <t>175122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205226</t>
+          <t>205415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59943</t>
+          <t>58527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81103</t>
+          <t>80170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54162</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76277</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119969</t>
+          <t>119238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150550</t>
+          <t>150200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15415</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15420</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29693</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6696</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69056</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90982</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>56376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>78601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131299</t>
+          <t>130173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161590</t>
+          <t>160885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,07%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49292</t>
+          <t>48818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>69655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58036</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78619</t>
+          <t>78342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110908</t>
+          <t>113255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142390</t>
+          <t>142319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>27669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38880</t>
+          <t>39629</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61139</t>
+          <t>62117</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>722</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>747</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>159248</t>
+          <t>158796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>190111</t>
+          <t>189840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>146506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>177312</t>
+          <t>178418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314395</t>
+          <t>316591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>361213</t>
+          <t>359336</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114366</t>
+          <t>114357</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144579</t>
+          <t>143664</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117848</t>
+          <t>118900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148280</t>
+          <t>147762</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241557</t>
+          <t>239399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283297</t>
+          <t>280912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22038</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39044</t>
+          <t>40111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32658</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>53498</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>59180</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85592</t>
+          <t>85692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>10911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13835</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07C18-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C18-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2007 (tasa de respuesta: 89,49%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la menor en 2007 (tasa de respuesta: 89,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53671</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44688</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>62942</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>52683</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>44058</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>61739</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>44926</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>60817</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>47,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53671</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>45513</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62697</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94647</t>
+          <t>94402</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118376</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44910</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37027</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53630</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,43%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43603</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35678</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51554</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>35066</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51606</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,03%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44910</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37311</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>53669</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76517</t>
+          <t>77713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99783</t>
+          <t>100331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19706</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14294</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27103</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,58%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,95%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>12764</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8262</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18913</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8091</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19017</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>11,43%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19706</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>13666</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>26452</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41968</t>
+          <t>40971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -1066,67 +1066,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1207</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4176</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4713</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1255</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7479</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1453</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5804</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123481</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55800</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46405</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>65771</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>67613</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57038</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77284</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57782</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77844</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>55800</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46451</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>66656</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>108473</t>
+          <t>110295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136896</t>
+          <t>139008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76034</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65772</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85493</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70710</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>60368</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>81896</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>60466</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>81424</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76034</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65268</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87521</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131755</t>
+          <t>130178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161486</t>
+          <t>160993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,43%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40028</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31701</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49788</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>17,17%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29762</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22893</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38165</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22407</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38071</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,75%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40028</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31404</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>49782</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57795</t>
+          <t>57767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82491</t>
+          <t>82726</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7468</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12773</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2077</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7468</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4078</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13130</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2613</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7501</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3997</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12600</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4196</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13677</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5328</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>184658</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>184658</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>184658</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>177663</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>177663</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>177663</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>184658</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>184658</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>184658</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>109471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95155</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>122129</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>120296</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>107153</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>133447</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>107469</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>133613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,12%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>109471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>95579</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>123528</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211827</t>
+          <t>211095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248763</t>
+          <t>248157</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>120944</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108067</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>135772</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114313</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>102148</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>127650</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101371</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128546</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,5%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>120944</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>107611</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>134636</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>215970</t>
+          <t>216072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253998</t>
+          <t>254585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>59733</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>48323</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70051</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>22,73%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>42526</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>33324</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>53354</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>33714</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>53389</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>14,7%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>59733</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>48978</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>71112</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>87718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117433</t>
+          <t>116482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8983</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4860</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14400</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3285</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1134</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7246</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8056</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>8983</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5182</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>15657</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9008</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14391</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>8954</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4899</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15142</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14422</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9008</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>5082</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14757</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>12032</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>308139</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>308139</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>308139</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>289374</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>289374</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>289374</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>308139</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>308139</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>308139</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la menor en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>92579</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81681</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101997</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>94985</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>84287</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>104175</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>84797</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>104497</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,62%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>92579</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>83025</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>103494</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173504</t>
+          <t>173091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201504</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>41730</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33186</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51957</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>21,66%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>38873</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30223</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49066</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30740</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48333</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>26,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41730</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>32941</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>50866</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69064</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>94791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11809</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7143</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>18579</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10621</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6399</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16736</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6469</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>16463</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,11%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11809</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7154</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19039</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15904</t>
+          <t>16445</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30948</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3342,67 +3342,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7018</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2884</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6553</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2797</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1947</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5179</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>4262</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8475</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>153178</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>153178</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>153178</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>149309</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>149309</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>149309</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>153178</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>153178</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>153178</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75985</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66034</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86370</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>79636</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>69378</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89813</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90140</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>75985</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>65979</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>86881</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140849</t>
+          <t>141150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170947</t>
+          <t>170118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70993</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59920</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>81904</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54975</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46070</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65165</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45094</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>65463</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70993</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>60258</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>80925</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>41,6%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112242</t>
+          <t>112159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>140893</t>
+          <t>141168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16918</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11420</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24340</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,26%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20190</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13878</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>28697</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13885</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27331</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,45%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,69%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16918</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10991</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23458</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28944</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>47152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7343</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2652</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7585</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6859</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1622</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7201</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3177</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7415</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4757</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2045</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9519</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9390</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,93%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3177</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6972</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>170651</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162209</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>170651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4367,67 +4367,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>168564</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>153997</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>183885</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>174620</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>160995</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189272</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>160300</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>190387</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,05%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>168564</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>153186</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>183035</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>321517</t>
+          <t>321868</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363346</t>
+          <t>363833</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>112723</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127900</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>34,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>93848</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>80531</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>106827</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>80346</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>107124</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>112723</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99083</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128469</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>188936</t>
+          <t>187958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227984</t>
+          <t>225611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28727</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20850</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>37565</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>30811</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22791</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>40350</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>22736</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>40306</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,89%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>12,95%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>28727</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20850</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>38003</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,87%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48450</t>
+          <t>48066</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>73489</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,51%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6376</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12861</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>5536</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2508</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11727</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2218</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10736</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6376</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3308</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11986</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7439</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12487</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>6703</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3390</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11733</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11672</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>7439</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>13342</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>471</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>323829</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>323829</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>323829</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>311518</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>323829</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>323829</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>323829</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado en 2016 (tasa de respuesta: 95,18%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la menor en 2016 (tasa de respuesta: 95,18%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>95469</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84596</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>106876</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,67%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,55%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>94728</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>84067</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>105355</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>83161</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>105399</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>53,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>95469</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>85542</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>106231</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,67%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175122</t>
+          <t>173502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205415</t>
+          <t>206511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,95%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64859</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>54859</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75241</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,84%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>42,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69865</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58527</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80170</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59824</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>81436</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>32,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64859</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>54401</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76554</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>118341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150200</t>
+          <t>150106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,12%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12533</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7821</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19361</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9595</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5849</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15624</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15517</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12533</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7409</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>18924</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30087</t>
+          <t>30176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3708</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8488</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8525</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>742</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6696</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6279</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2826</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5642</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>177898</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177898</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>177898</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>178459</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>178459</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>178459</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>177898</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177898</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>177898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66720</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56274</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>78558</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33,13%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>79422</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>68578</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>91096</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>68401</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90079</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>66720</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>56376</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>78601</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130173</t>
+          <t>131557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>160992</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,1%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67727</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56745</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77978</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>39,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>59220</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48818</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69655</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>48741</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70057</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>35,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67727</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57214</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78342</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113255</t>
+          <t>112091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142319</t>
+          <t>142095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,46%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29387</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21267</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>20145</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14050</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27669</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14015</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27868</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29387</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21589</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>38787</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>17,3%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>39330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62117</t>
+          <t>61497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,37%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7017</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3939</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8885</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8339</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2893</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3152</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8009</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2081</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5617</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>7442</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169879</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169879</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169879</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164807</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>169879</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>169879</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>169879</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>162189</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>144923</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>177404</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>174150</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>158796</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>189840</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>156822</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>188381</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>162189</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>146506</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>178418</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>316591</t>
+          <t>315735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>359336</t>
+          <t>360523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>132586</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>119738</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>150906</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>129084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114357</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143664</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114555</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>33,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>132586</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>118900</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147762</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239399</t>
+          <t>240782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280912</t>
+          <t>282738</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41921</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32375</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52730</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12,05%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>29739</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22442</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>40111</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>21864</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>38750</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,66%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>41921</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32658</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>53498</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>12,05%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>58631</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85692</t>
+          <t>85006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5830</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11448</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>7646</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12803</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4190</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13356</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5830</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10911</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8262</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>20784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5251</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2384</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10757</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2645</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6605</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>833</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7067</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5251</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2204</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>10086</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>347776</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>347776</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>347776</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>489</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>343266</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>343266</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>343266</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>347776</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>347776</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>347776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
